--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_62_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_62_R7.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5314</v>
+        <v>8.9505</v>
       </c>
       <c r="E2" t="n">
-        <v>6.585</v>
+        <v>6.5418</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9464</v>
+        <v>2.4087</v>
       </c>
       <c r="G2" t="n">
         <v>6.6567</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1273</v>
+        <v>0.5463</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1142</v>
+        <v>0.0709</v>
       </c>
       <c r="U2" t="n">
-        <v>1.013</v>
+        <v>0.4753</v>
       </c>
       <c r="V2" t="n">
         <v>0.8197</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.45</v>
+        <v>3.1819</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5215</v>
+        <v>-0.2856</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9715</v>
+        <v>3.4674</v>
       </c>
       <c r="G3" t="n">
         <v>0.5222</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6032</v>
+        <v>0.335</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9766</v>
+        <v>0.4725</v>
       </c>
       <c r="V3" t="n">
         <v>1.8608</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0279</v>
+        <v>1.5981</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6057</v>
+        <v>-1.2323</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6336</v>
+        <v>2.8303</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9685</v>
+        <v>1.0016</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9183</v>
+        <v>-0.2064</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0502</v>
+        <v>1.208</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4369</v>
+        <v>-0.0205</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4871</v>
+        <v>-0.131</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0502</v>
+        <v>0.1104</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4683</v>
+        <v>1.0222</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5688</v>
+        <v>-0.0755</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1005</v>
+        <v>1.0976</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0154</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7552</v>
+        <v>0.452</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0272</v>
+        <v>0.0356</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7824</v>
+        <v>0.4165</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1203</v>
+        <v>1.5881</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3125</v>
+        <v>-0.8102</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4328</v>
+        <v>2.3983</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004</v>
+        <v>1.9685</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6554</v>
+        <v>1.9183</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6595</v>
+        <v>0.0502</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1865</v>
+        <v>2.4369</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9509</v>
+        <v>2.4871</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1374</v>
+        <v>-0.0502</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1825</v>
+        <v>-0.4683</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7045</v>
+        <v>-0.5688</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5221</v>
+        <v>0.1005</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.6959</v>
+        <v>-3.0154</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0435</v>
+        <v>0.3154</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1968</v>
+        <v>-0.2317</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2403</v>
+        <v>0.5472</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.091</v>
+        <v>1.1943</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8074</v>
+        <v>-0.4737</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8983</v>
+        <v>1.6681</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3324</v>
+        <v>0.004</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0432</v>
+        <v>-1.6554</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3756</v>
+        <v>1.6595</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9929</v>
+        <v>0.1865</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9677</v>
+        <v>-0.9509</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9606</v>
+        <v>1.1374</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3396</v>
+        <v>-0.1825</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0755</v>
+        <v>-0.7045</v>
       </c>
       <c r="O6" t="n">
-        <v>0.415</v>
+        <v>0.5221</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8307</v>
+        <v>0.0305</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1766</v>
+        <v>0.0356</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0073</v>
+        <v>-0.005</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4721</v>
+        <v>1.1634</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0893</v>
+        <v>-0.7013</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5615</v>
+        <v>1.8647</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0016</v>
+        <v>1.3324</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2064</v>
+        <v>-1.0432</v>
       </c>
       <c r="I7" t="n">
-        <v>1.208</v>
+        <v>2.3756</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0205</v>
+        <v>0.9929</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.131</v>
+        <v>-0.9677</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1104</v>
+        <v>1.9606</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0222</v>
+        <v>0.3396</v>
       </c>
       <c r="N7" t="n">
         <v>-0.0755</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0976</v>
+        <v>0.415</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-1.6237</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6739000000000001</v>
+        <v>0.9032</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8215</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1476</v>
+        <v>0.9737</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4213</v>
+        <v>0.8081</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.202</v>
+        <v>-1.084</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6233</v>
+        <v>1.8921</v>
       </c>
       <c r="G8" t="n">
         <v>0.8552999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1299</v>
+        <v>-0.7431</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6071</v>
+        <v>-0.3383</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3052</v>
+        <v>-0.3549</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4761</v>
+        <v>-2.2645</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7814</v>
+        <v>1.9095</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4684</v>
+        <v>0.4252</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2414</v>
+        <v>2.0347</v>
       </c>
       <c r="I9" t="n">
-        <v>0.773</v>
+        <v>-1.6095</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8722</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0194</v>
+        <v>2.7931</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472</v>
+        <v>-2.1283</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4039</v>
+        <v>-0.2397</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.222</v>
+        <v>-0.7584</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6258</v>
+        <v>0.5188</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>2.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8458</v>
+        <v>0.1709</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5558</v>
+        <v>-0.2671</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2899</v>
+        <v>0.438</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>-1.1829</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.1107</v>
       </c>
       <c r="X9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.118</v>
+        <v>-1.0623</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9603</v>
+        <v>-1.9781</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8423</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4252</v>
+        <v>-1.4684</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0347</v>
+        <v>-2.2414</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6095</v>
+        <v>0.773</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6647999999999999</v>
+        <v>-1.8722</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7931</v>
+        <v>-2.0194</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1283</v>
+        <v>0.1472</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2397</v>
+        <v>0.4039</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7584</v>
+        <v>-0.222</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5188</v>
+        <v>0.6258</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7834</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5921999999999999</v>
+        <v>1.4782</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.963</v>
+        <v>1.0539</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3708</v>
+        <v>0.4244</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1829</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1107</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.0722</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U. PLAVSIC</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6416</v>
+        <v>-2.1603</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8248</v>
+        <v>-2.7504</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8168</v>
+        <v>0.5901</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9833</v>
+        <v>-1.1274</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6722</v>
+        <v>-1.4585</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3111</v>
+        <v>0.3311</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1104</v>
+        <v>-1.1309</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1104</v>
+        <v>-0.3984</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0938</v>
+        <v>0.0035</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6722</v>
+        <v>-0.7261</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4216</v>
+        <v>0.7296</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.5515</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7834</v>
+        <v>-1.6237</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1046</v>
+        <v>0.5032</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>0.0042</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3286</v>
+        <v>0.4991</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7886</v>
+        <v>-1.0722</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>U. PLAVSIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4639</v>
+        <v>-2.5909</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6507</v>
+        <v>-1.7069</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1868</v>
+        <v>-0.884</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1274</v>
+        <v>-0.9833</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4585</v>
+        <v>-0.6722</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3311</v>
+        <v>-0.3111</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1309</v>
+        <v>0.1104</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7324000000000001</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3984</v>
+        <v>0.1104</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0035</v>
+        <v>-1.0938</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7261</v>
+        <v>-0.6722</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7296</v>
+        <v>-0.4216</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.6237</v>
+        <v>-2.7834</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8004</v>
+        <v>0.1553</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8962</v>
+        <v>-0.1061</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0958</v>
+        <v>0.2614</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0722</v>
+        <v>0.7886</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.1957</v>
+        <v>12.316</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.8653</v>
+        <v>-6.7452</v>
       </c>
       <c r="F13" t="n">
-        <v>19.0611</v>
+        <v>19.061</v>
       </c>
       <c r="G13" t="n">
         <v>9.1868</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6287</v>
+        <v>2.628699999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>6.558200000000001</v>
+        <v>6.5582</v>
       </c>
       <c r="J13" t="n">
         <v>7.990599999999999</v>
@@ -1447,13 +1447,13 @@
         <v>7.422700000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5678</v>
+        <v>0.5677999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>1.1965</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.794199999999999</v>
+        <v>-4.7942</v>
       </c>
       <c r="O13" t="n">
         <v>5.990500000000001</v>
@@ -1468,13 +1468,13 @@
         <v>18.5563</v>
       </c>
       <c r="S13" t="n">
-        <v>3.026899999999999</v>
+        <v>4.1469</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1379</v>
+        <v>-0.01749999999999997</v>
       </c>
       <c r="U13" t="n">
-        <v>4.164599999999999</v>
+        <v>4.1648</v>
       </c>
       <c r="V13" t="n">
         <v>0.1417999999999997</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8083</v>
+        <v>2.5223</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3338</v>
+        <v>0.2159</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4745</v>
+        <v>2.3065</v>
       </c>
       <c r="G14" t="n">
         <v>1.0392</v>
@@ -1546,13 +1546,13 @@
         <v>3.0154</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4266</v>
+        <v>-0.7125</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4086</v>
+        <v>-0.5265</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.018</v>
+        <v>-0.186</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8197</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9229</v>
+        <v>1.7371</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5561</v>
+        <v>0.2022</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3668</v>
+        <v>1.5349</v>
       </c>
       <c r="G15" t="n">
         <v>0.1635</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3282</v>
+        <v>-0.514</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1889</v>
+        <v>-0.165</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5171</v>
+        <v>-0.349</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3926</v>
+        <v>1.6456</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3067</v>
+        <v>0.6605</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0859</v>
+        <v>0.9851</v>
       </c>
       <c r="G16" t="n">
         <v>-1.058</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8536</v>
+        <v>-0.6005</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2696</v>
+        <v>-0.9157</v>
       </c>
       <c r="U16" t="n">
-        <v>0.416</v>
+        <v>0.3152</v>
       </c>
       <c r="V16" t="n">
         <v>2.1444</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1456</v>
+        <v>0.0105</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0324</v>
+        <v>-0.2684</v>
       </c>
       <c r="F17" t="n">
-        <v>0.178</v>
+        <v>0.2788</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5507</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2315</v>
+        <v>-0.3666</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0395</v>
+        <v>-0.1964</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.271</v>
+        <v>-0.1702</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8337</v>
+        <v>-0.7272</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0902</v>
+        <v>-1.2081</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2564</v>
+        <v>0.4809</v>
       </c>
       <c r="G18" t="n">
         <v>0.1002</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4701</v>
+        <v>-0.3635</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4832</v>
+        <v>-0.6012</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0132</v>
+        <v>0.2377</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3974</v>
+        <v>-1.4139</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7996</v>
+        <v>-0.6816</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5978</v>
+        <v>-0.7322</v>
       </c>
       <c r="G19" t="n">
         <v>0.4938</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1722</v>
+        <v>-0.1887</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4999</v>
+        <v>0.3655</v>
       </c>
       <c r="V19" t="n">
         <v>-1.719</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0412</v>
+        <v>-1.9949</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6375</v>
+        <v>-3.301</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5962</v>
+        <v>1.3061</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3135</v>
+        <v>-2.5275</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8054</v>
+        <v>-1.0286</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4919</v>
+        <v>-1.499</v>
       </c>
       <c r="J20" t="n">
-        <v>0.645</v>
+        <v>-0.1787</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5714</v>
+        <v>1.21</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>-1.3887</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9584</v>
+        <v>-2.3488</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3767</v>
+        <v>-2.2385</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4183</v>
+        <v>-0.1103</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.4639</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-3.4793</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-4.639</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>3.0154</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7515</v>
+        <v>-0.3282</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3566</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3949</v>
+        <v>0.387</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.3247</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5116</v>
+        <v>-2.405</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5382</v>
+        <v>-4.6561</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0266</v>
+        <v>2.2511</v>
       </c>
       <c r="G21" t="n">
         <v>-3.724</v>
@@ -2092,13 +2092,13 @@
         <v>2.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4112</v>
+        <v>-0.3047</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2513</v>
+        <v>-0.3692</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1599</v>
+        <v>0.0646</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8256</v>
+        <v>-2.7083</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7728</v>
+        <v>-3.8133</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9472</v>
+        <v>1.105</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5275</v>
+        <v>-0.4073</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0286</v>
+        <v>0.6735</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.499</v>
+        <v>-1.0808</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1787</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>1.21</v>
+        <v>1.0958</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3887</v>
+        <v>-1.1813</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3488</v>
+        <v>-0.3219</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.2385</v>
+        <v>-0.4223</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1103</v>
+        <v>0.1005</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-4.639</v>
       </c>
       <c r="R22" t="n">
-        <v>3.0154</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1589</v>
+        <v>0.1061</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.187</v>
+        <v>-0.161</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0281</v>
+        <v>0.2671</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3247</v>
+        <v>1.0722</v>
       </c>
       <c r="W22" t="n">
         <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2194</v>
+        <v>-2.8777</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1671</v>
+        <v>-3.4631</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9477</v>
+        <v>0.5855</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4073</v>
+        <v>-0.3135</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6735</v>
+        <v>-0.8054</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0808</v>
+        <v>0.4919</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.08550000000000001</v>
+        <v>0.645</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0958</v>
+        <v>0.5714</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1813</v>
+        <v>0.0736</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3219</v>
+        <v>-0.9584</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4223</v>
+        <v>-1.3767</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1005</v>
+        <v>0.4183</v>
       </c>
       <c r="P23" t="n">
         <v>-3.4793</v>
@@ -2248,19 +2248,19 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.405</v>
+        <v>0.9151</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5149</v>
+        <v>0.5309</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1098</v>
+        <v>0.3842</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6362</v>
+        <v>-4.198</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.22</v>
+        <v>-2.7481</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4162</v>
+        <v>-1.4498</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4026</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3211</v>
+        <v>0.1171</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.963</v>
+        <v>-0.4911</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6418</v>
+        <v>0.6082</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1444</v>
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.1957</v>
+        <v>-10.4095</v>
       </c>
       <c r="E25" t="n">
-        <v>-19.0612</v>
+        <v>-19.0611</v>
       </c>
       <c r="F25" t="n">
-        <v>7.8653</v>
+        <v>8.651899999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-9.186900000000001</v>
+        <v>-9.1869</v>
       </c>
       <c r="H25" t="n">
         <v>-2.6286</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.5584</v>
+        <v>-6.558399999999999</v>
       </c>
       <c r="J25" t="n">
         <v>-1.1964</v>
       </c>
       <c r="K25" t="n">
-        <v>4.7942</v>
+        <v>4.794200000000001</v>
       </c>
       <c r="L25" t="n">
         <v>-5.990600000000001</v>
@@ -2392,10 +2392,10 @@
         <v>-7.422600000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5678</v>
+        <v>-0.5677999999999997</v>
       </c>
       <c r="P25" t="n">
-        <v>1.159900000000001</v>
+        <v>1.1599</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.5562</v>
@@ -2404,13 +2404,13 @@
         <v>19.7161</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.0269</v>
+        <v>-2.2404</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.1647</v>
+        <v>-4.1646</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1377</v>
+        <v>1.9243</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1417999999999999</v>
